--- a/data/trans_orig/P13A_1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) en 2023</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26806</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25605</t>
+          <t>26330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284647</t>
+          <t>282072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306401</t>
+          <t>306376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>685835</t>
+          <t>685110</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>706729</t>
+          <t>706510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>15809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23536</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409872</t>
+          <t>410064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422305</t>
+          <t>422473</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495780</t>
+          <t>495536</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508052</t>
+          <t>508230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911356</t>
+          <t>913692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928560</t>
+          <t>928631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25833</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16409</t>
+          <t>16953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34796</t>
+          <t>34250</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518342</t>
+          <t>518584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531281</t>
+          <t>531218</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>513595</t>
+          <t>514864</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>527462</t>
+          <t>527684</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1038607</t>
+          <t>1039153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1056994</t>
+          <t>1056450</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30715</t>
+          <t>31046</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60368</t>
+          <t>60373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27872</t>
+          <t>27368</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67684</t>
+          <t>67966</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>870859</t>
+          <t>871511</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>884840</t>
+          <t>884749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>650326</t>
+          <t>650321</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>679979</t>
+          <t>679648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1529720</t>
+          <t>1529438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1569532</t>
+          <t>1570036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>17887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>21886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37834</t>
+          <t>37952</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30826</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50933</t>
+          <t>51496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>539734</t>
+          <t>539714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>552447</t>
+          <t>552215</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>506409</t>
+          <t>506291</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>521817</t>
+          <t>522357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1050911</t>
+          <t>1050348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1071018</t>
+          <t>1070981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>28114</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29032</t>
+          <t>30578</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>356048</t>
+          <t>356390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>363644</t>
+          <t>363579</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>579365</t>
+          <t>579137</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>600772</t>
+          <t>600787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>943387</t>
+          <t>941841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>963541</t>
+          <t>962371</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25044</t>
+          <t>24742</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>30074</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>271528</t>
+          <t>271841</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>278784</t>
+          <t>278921</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>398891</t>
+          <t>399193</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>411195</t>
+          <t>411100</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>674563</t>
+          <t>674940</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>688774</t>
+          <t>688632</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51787</t>
+          <t>51393</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118711</t>
+          <t>116137</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>173404</t>
+          <t>172756</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152673</t>
+          <t>153163</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211370</t>
+          <t>211769</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3396281</t>
+          <t>3396675</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3422966</t>
+          <t>3422865</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3474944</t>
+          <t>3475592</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3529637</t>
+          <t>3532211</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6885046</t>
+          <t>6884647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6943743</t>
+          <t>6943253</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13A_1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_R-Edad-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29381</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26330</t>
+          <t>34341</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>298687</t>
+          <t>342554</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282072</t>
+          <t>327107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306376</t>
+          <t>351965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>698674</t>
+          <t>750348</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>685110</t>
+          <t>732066</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>706510</t>
+          <t>759568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>311453</t>
+          <t>358613</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>311453</t>
+          <t>358613</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311453</t>
+          <t>358613</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>711440</t>
+          <t>766407</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>711440</t>
+          <t>766407</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>711440</t>
+          <t>766407</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>18088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21200</t>
+          <t>23918</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>419113</t>
+          <t>471486</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410064</t>
+          <t>462429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422473</t>
+          <t>475512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>503632</t>
+          <t>491184</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495536</t>
+          <t>482020</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508230</t>
+          <t>495859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>922745</t>
+          <t>962670</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>913692</t>
+          <t>953080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928631</t>
+          <t>969621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511345</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511345</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511345</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934892</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934892</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934892</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,102 +1411,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>18743</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12484</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26507</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>25865</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>17527</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>35638</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>2,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17497</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11744</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24564</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>24476</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>16953</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>34250</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1524,102 +1524,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>526996</t>
+          <t>610284</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518584</t>
+          <t>601863</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531218</t>
+          <t>614605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>97,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>600123</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>592359</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>606382</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1210407</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1200634</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1218745</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>97,12%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>521931</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>514864</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>527684</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1048927</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1039153</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1056450</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533975</t>
+          <t>617406</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533975</t>
+          <t>617406</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533975</t>
+          <t>617406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>539428</t>
+          <t>618866</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>539428</t>
+          <t>618866</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>539428</t>
+          <t>618866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1073403</t>
+          <t>1236272</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1073403</t>
+          <t>1236272</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1073403</t>
+          <t>1236272</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>41031</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>32247</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60373</t>
+          <t>51354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48905</t>
+          <t>48423</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27368</t>
+          <t>37497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67966</t>
+          <t>61838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>879477</t>
+          <t>692128</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>871511</t>
+          <t>683996</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>884749</t>
+          <t>696392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>669023</t>
+          <t>692995</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>650321</t>
+          <t>682672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>679648</t>
+          <t>701779</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1548499</t>
+          <t>1385123</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1529438</t>
+          <t>1371708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1570036</t>
+          <t>1396049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>710694</t>
+          <t>734026</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>710694</t>
+          <t>734026</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>710694</t>
+          <t>734026</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1597404</t>
+          <t>1433546</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1597404</t>
+          <t>1433546</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1597404</t>
+          <t>1433546</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17887</t>
+          <t>18924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29562</t>
+          <t>32439</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21886</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37952</t>
+          <t>42425</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>43455</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>33750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51496</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>547418</t>
+          <t>594474</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>539714</t>
+          <t>586566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>552215</t>
+          <t>599719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>514681</t>
+          <t>572426</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>506291</t>
+          <t>562440</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>522357</t>
+          <t>580781</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1062099</t>
+          <t>1166900</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1050348</t>
+          <t>1155096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1070981</t>
+          <t>1176605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>557601</t>
+          <t>605490</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>557601</t>
+          <t>605490</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>557601</t>
+          <t>605490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544243</t>
+          <t>604865</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544243</t>
+          <t>604865</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544243</t>
+          <t>604865</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1101844</t>
+          <t>1210355</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1101844</t>
+          <t>1210355</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1101844</t>
+          <t>1210355</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28114</t>
+          <t>25648</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>361222</t>
+          <t>399595</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>356390</t>
+          <t>394863</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>363579</t>
+          <t>402102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>590844</t>
+          <t>420283</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>579137</t>
+          <t>412316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>600787</t>
+          <t>425266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>952066</t>
+          <t>819878</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>941841</t>
+          <t>812352</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>962371</t>
+          <t>826169</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>365168</t>
+          <t>403628</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>365168</t>
+          <t>403628</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>365168</t>
+          <t>403628</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607251</t>
+          <t>437964</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607251</t>
+          <t>437964</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607251</t>
+          <t>437964</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>972419</t>
+          <t>841592</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>972419</t>
+          <t>841592</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>972419</t>
+          <t>841592</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>10033</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12835</t>
+          <t>14401</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>28148</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>25145</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>18217</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30074</t>
+          <t>35022</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>276461</t>
+          <t>303347</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>271841</t>
+          <t>298256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>278921</t>
+          <t>306025</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>406057</t>
+          <t>442472</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>399193</t>
+          <t>434527</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>411100</t>
+          <t>448274</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>682518</t>
+          <t>745819</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>674940</t>
+          <t>735942</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>688632</t>
+          <t>752747</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281079</t>
+          <t>308289</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281079</t>
+          <t>308289</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281079</t>
+          <t>308289</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423935</t>
+          <t>462675</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423935</t>
+          <t>462675</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>423935</t>
+          <t>462675</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>705014</t>
+          <t>770964</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>705014</t>
+          <t>770964</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705014</t>
+          <t>770964</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51393</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>143493</t>
+          <t>155081</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116137</t>
+          <t>135676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>172756</t>
+          <t>179204</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>153163</t>
+          <t>168200</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211769</t>
+          <t>222488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3410675</t>
+          <t>3479108</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3396675</t>
+          <t>3463463</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3422865</t>
+          <t>3489747</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3504855</t>
+          <t>3562037</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3475592</t>
+          <t>3537914</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3532211</t>
+          <t>3581442</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6915529</t>
+          <t>7041145</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6884647</t>
+          <t>7013646</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6943253</t>
+          <t>7067934</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
